--- a/ig/specifications_techniques/ValueSet-EyeColorVS.xlsx
+++ b/ig/specifications_techniques/ValueSet-EyeColorVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-11T11:43:09+00:00</t>
+    <t>2023-09-11T14:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/ValueSet-EyeColorVS.xlsx
+++ b/ig/specifications_techniques/ValueSet-EyeColorVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-11T14:46:38+00:00</t>
+    <t>2023-09-12T10:01:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
